--- a/programs/athletic-strength/access-f004f91b98/VOLTR-Athletic-Strength.xlsx
+++ b/programs/athletic-strength/access-f004f91b98/VOLTR-Athletic-Strength.xlsx
@@ -712,7 +712,7 @@
       <c r="A2" s="3" t="n"/>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8 weeks  ·  3 sessions per week  ·  60 to 75 minutes  ·  full gym</t>
+          <t>8 weeks  ·  3 sessions per week  ·  60 to 80 minutes  ·  full gym</t>
         </is>
       </c>
       <c r="D2" s="3" t="n"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Eight weeks, three sessions a week, 60 to 75 minutes each. Each session starts with power work while you are fresh, then one heavy compound lift, paired accessories, trunk work and a loaded carry. Two blocks: block 1 builds volume, block 2 lowers reps and raises load. Week 1 and week 8 are measured.</t>
+          <t>Eight weeks, three sessions a week, 60 to 80 minutes each. Each session starts with power work while you are fresh, then one heavy compound lift, paired accessories, trunk work and a loaded carry. Two blocks: block 1 builds volume, block 2 lowers reps and raises load. Week 1 and week 8 are measured.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
           <t>Main lifts (squat, bench press, trap bar deadlift): linear load progression. Week 1 sets the load. Then add 2.5 to 5 kg on squat and deadlift, 1 to 2.5 kg on bench, each week the previous sets matched the target RIR. If not, repeat the load.
 Accessories: double progression. When all sets reach the top of the rep range at the target RIR, add the smallest step and start at the bottom again.
 Power work: every rep at maximal intent. End the set when height, distance or speed drops.
-Week 4: deload, fewer sets, week-2 loads, RIR 3 to 4. Block 2 starts with roughly your week 3 loads at lower reps. Week 8 is the test: one top set at RPE 9, two back-off sets, top set into the e1RM table on the LOG tab.</t>
+Week 4: deload, fewer sets, week-2 loads, RIR 3 to 4. Block 2 starts with roughly your week 3 loads at lower reps. Week 1 opens each main lift with a benchmark top set of 5 at RIR 2. Week 8 is the test: one top set of 3 at RPE 9, two back-off sets. Both top sets go into the e1RM table on the LOG tab.</t>
         </is>
       </c>
     </row>
@@ -874,11 +874,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>1:1 coaching builds the program around your schedule, travel and training history. Book a 30-minute call: https://calendly.com/training-voltr/30min</t>
+          <t>1:1 coaching builds the program around your schedule, travel and training history. Book a 30-minute call: https://voltr.at/#book</t>
         </is>
       </c>
       <c r="D16" s="7" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -944,7 +945,7 @@
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>Block 1 builds the volume that block 2 turns into heavier lifting. Each session opens with power work, then one main lift, then accessories, trunk and a carry. Main lifts: add load each week as long as the target RIR holds. Week 4 is the deload: fewer sets, week-2 loads, RIR 3 to 4. Order of sessions: A, B, C.</t>
+          <t>Block 1 builds the volume that block 2 turns into heavier lifting. Each session opens with power work, then one main lift, then accessories, trunk and a carry. Main lifts: add load each week as long as the target RIR holds. Week 4 is the deload: fewer sets, week-2 loads, RIR 3 to 4. Week 1 includes the benchmarks: broad jump, main-lift top sets, max chin-ups and the farmer carry test. Order of sessions: A, B, C.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>3 x 3</t>
+          <t>Broad jump test: best of 3 (benchmark), then 3 x 3</t>
         </is>
       </c>
       <c r="G8" s="26" t="n"/>
@@ -1141,7 +1142,7 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>4 x 6 @ RIR 3</t>
+          <t>Top set 1 x 5 @ RIR 2 (benchmark), then 3 x 6 @ RIR 3</t>
         </is>
       </c>
       <c r="G9" s="26" t="n"/>
@@ -1243,7 +1244,7 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>4 x 5-8 @ RIR 3</t>
+          <t>Set 1: max strict reps (benchmark), then 3 x 5-8 @ RIR 3</t>
         </is>
       </c>
       <c r="G11" s="26" t="n"/>
@@ -1465,7 +1466,7 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>4 x 6 @ RIR 3</t>
+          <t>Top set 1 x 5 @ RIR 2 (benchmark), then 3 x 6 @ RIR 3</t>
         </is>
       </c>
       <c r="G17" s="26" t="n"/>
@@ -1844,7 +1845,7 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>4 x 5 @ RIR 3</t>
+          <t>Top set 1 x 5 @ RIR 2 (benchmark), then 3 x 5 @ RIR 3</t>
         </is>
       </c>
       <c r="G26" s="26" t="n"/>
@@ -2044,7 +2045,7 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>4 x 30 m</t>
+          <t>Test: heaviest pair for 30 m (benchmark), then 3 x 30 m</t>
         </is>
       </c>
       <c r="G30" s="26" t="n"/>
@@ -2114,6 +2115,7 @@
       </c>
       <c r="M31" s="28" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33" ht="22" customHeight="1">
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -2187,7 +2189,7 @@
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>Block 2 keeps the three main lifts and moves to lower reps and heavier loads. Power work and several accessories change. Start week 5 on the main lifts with roughly your week 3 loads. Week 8 is the test: build to one top set at RPE 9, then two back-off sets at RIR 3. Write the top sets into the benchmarks on the LOG tab.</t>
+          <t>Block 2 keeps the three main lifts and moves to lower reps and heavier loads. Power work and several accessories change. Start week 5 on the main lifts with roughly your week 3 loads. Week 8 is the test: build to one top set of 3 at RPE 9, then two back-off sets at RIR 3. Broad jump, chin-up and farmer carry tests sit in the same sessions as in week 1. Write the top sets into the benchmarks on the LOG tab.</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2353,7 @@
       <c r="K8" s="26" t="n"/>
       <c r="L8" s="27" t="inlineStr">
         <is>
-          <t>3 x 2</t>
+          <t>Test: best of 3 (benchmark)</t>
         </is>
       </c>
       <c r="M8" s="28" t="n"/>
@@ -2402,7 +2404,7 @@
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="inlineStr">
         <is>
-          <t>Top set 1 x 2 @ RPE 9, then 2 x 4 @ RIR 3</t>
+          <t>Top set 1 x 3 @ RPE 9, then 2 x 4 @ RIR 3</t>
         </is>
       </c>
       <c r="M9" s="28" t="n"/>
@@ -2504,7 +2506,7 @@
       <c r="K11" s="26" t="n"/>
       <c r="L11" s="27" t="inlineStr">
         <is>
-          <t>2 x 4 @ RIR 3</t>
+          <t>Set 1: max strict reps at bodyweight (benchmark), then 1 x 4 @ RIR 3</t>
         </is>
       </c>
       <c r="M11" s="28" t="n"/>
@@ -2726,7 +2728,7 @@
       <c r="K17" s="26" t="n"/>
       <c r="L17" s="27" t="inlineStr">
         <is>
-          <t>Top set 1 x 2 @ RPE 9, then 2 x 4 @ RIR 3</t>
+          <t>Top set 1 x 3 @ RPE 9, then 2 x 4 @ RIR 3</t>
         </is>
       </c>
       <c r="M17" s="28" t="n"/>
@@ -3105,7 +3107,7 @@
       <c r="K26" s="26" t="n"/>
       <c r="L26" s="27" t="inlineStr">
         <is>
-          <t>Top set 1 x 2 @ RPE 9, then 2 x 3 @ RIR 3</t>
+          <t>Top set 1 x 3 @ RPE 9, then 2 x 3 @ RIR 3</t>
         </is>
       </c>
       <c r="M26" s="28" t="n"/>
@@ -3305,7 +3307,7 @@
       <c r="K30" s="26" t="n"/>
       <c r="L30" s="27" t="inlineStr">
         <is>
-          <t>2 x 20 m</t>
+          <t>Test: heaviest pair for 30 m (benchmark)</t>
         </is>
       </c>
       <c r="M30" s="28" t="n"/>
@@ -3357,6 +3359,7 @@
       </c>
       <c r="M31" s="28" t="n"/>
     </row>
+    <row r="32"/>
     <row r="33" ht="22" customHeight="1">
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -3424,6 +3427,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -3528,6 +3532,8 @@
       <c r="G14" s="34" t="n"/>
       <c r="H14" s="34" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="31" t="inlineStr">
         <is>
@@ -3565,7 +3571,7 @@
       </c>
       <c r="H19" s="38" t="inlineStr">
         <is>
-          <t>Enter load x reps @ RIR (e.g. 100 x 5 @ 2). Week 1: best set of the week. Week 8: top set. The e1RM table below compares both on one scale.</t>
+          <t>Enter load x reps @ RIR (e.g. 100 x 5 @ 2). Week 1: the benchmark top set. Week 8: the test top set. The e1RM table below compares both on one scale.</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3607,7 @@
       </c>
       <c r="H22" s="38" t="inlineStr">
         <is>
-          <t>After the warm-up, three jumps with full rest. Measure from the start line to the back heel. Best of three.</t>
+          <t>Day A, before the box jumps (week 1) or as the broad jump sets (week 8). Three jumps with full rest. Measure from the start line to the back heel. Best of three.</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3619,7 @@
       </c>
       <c r="H23" s="38" t="inlineStr">
         <is>
-          <t>Bodyweight, full hang to chin over the bar, no swing. One set, at the start of Day A.</t>
+          <t>Bodyweight, full hang to chin over the bar, no swing. First chin-up set on Day A in week 1 and week 8.</t>
         </is>
       </c>
     </row>
@@ -3625,13 +3631,15 @@
       </c>
       <c r="H24" s="38" t="inlineStr">
         <is>
-          <t>Heaviest pair carried 30 m without putting it down or losing posture.</t>
-        </is>
-      </c>
-    </row>
+          <t>Day C, in place of the first farmer carry set. Heaviest pair carried 30 m without putting it down or losing posture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="10" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="31" t="inlineStr">
         <is>
@@ -3773,6 +3781,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="46" t="inlineStr">
         <is>
